--- a/sources/kazuya_step10.xlsx
+++ b/sources/kazuya_step10.xlsx
@@ -893,6 +893,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>06b27057-ba76-403e-85c6-5241d4d27973</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr">
         <is>
           <t>06b27057-ba76-403e-85c6-5241d4d27973</t>
@@ -950,6 +955,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>22c62dd3-2f75-4092-bad9-4baa879dd867</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr">
         <is>
           <t>22c62dd3-2f75-4092-bad9-4baa879dd867</t>
@@ -1012,6 +1022,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>5693325a-9d43-4c1e-9f0a-37293eb4860d</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr">
         <is>
           <t>5693325a-9d43-4c1e-9f0a-37293eb4860d</t>
@@ -1084,6 +1099,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>d51fee9f-9d4e-4225-aa39-2f2d2e364398</t>
+        </is>
+      </c>
       <c r="AB9" t="inlineStr">
         <is>
           <t>d51fee9f-9d4e-4225-aa39-2f2d2e364398</t>
@@ -1151,6 +1171,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>9463b80f-225a-4a7a-b350-0a3008c72604</t>
+        </is>
+      </c>
       <c r="AB10" t="inlineStr">
         <is>
           <t>9463b80f-225a-4a7a-b350-0a3008c72604</t>
@@ -1216,6 +1241,11 @@
       <c r="W11" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>cc572ca8-7e2b-4695-be36-969d95d53b5c</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -7569,6 +7599,11 @@
           <t>hh"hh"mm"Lhmm</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>a1af16e4-84f3-4abd-b887-4c65bc756223</t>
+        </is>
+      </c>
       <c r="AB81" t="inlineStr">
         <is>
           <t>a1af16e4-84f3-4abd-b887-4c65bc756223</t>
@@ -7621,6 +7656,11 @@
           <t>hh'hh"mm"LL"m!</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>1abe1117-e220-4cde-b7c9-6a59e7c16e8d</t>
+        </is>
+      </c>
       <c r="AB82" t="inlineStr">
         <is>
           <t>1abe1117-e220-4cde-b7c9-6a59e7c16e8d</t>
@@ -7671,6 +7711,11 @@
       <c r="U83" t="inlineStr">
         <is>
           <t>hh"mm"sm"L"m!</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>ca41b863-8414-4a05-af5c-d5d050d26435</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">

--- a/sources/kazuya_step10.xlsx
+++ b/sources/kazuya_step10.xlsx
@@ -417,39 +417,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD83"/>
+  <dimension ref="A1:AE83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col hidden="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col hidden="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col hidden="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col hidden="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col hidden="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col hidden="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col hidden="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col hidden="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="132" customWidth="1" min="25" max="25"/>
-    <col width="10" customWidth="1" min="26" max="26"/>
-    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col hidden="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col hidden="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col hidden="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col hidden="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col hidden="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col hidden="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col hidden="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="132" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
     <col width="38" customWidth="1" min="28" max="28"/>
     <col width="38" customWidth="1" min="29" max="29"/>
-    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="38" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,130 +483,135 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC2" s="1" t="inlineStr">
+      <c r="AD2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD2" s="1" t="inlineStr">
+      <c r="AE2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -622,62 +628,62 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Bitch Kicks</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Bitch Kicks</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>2f12b8ca-b142-48da-921e-5b363f240589</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>13eb04cf-3cdd-4e0d-b0b0-59f08160f5a4</t>
         </is>
@@ -694,62 +700,62 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Hip Toss</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Hip Toss</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>915fef12-186f-4bfa-aa77-19b2f16da957</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>02170733-7247-478d-b6e4-20237571838b</t>
         </is>
@@ -766,72 +772,72 @@
           <t>f,f+1+2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Stone Head</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Stone Head</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Opponent can tech roll after the throw.; Special Tag Throw with Jun only. Jun finishes with a Reverse Arm Bar. Total damage is 30.</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>e06b7141-62e9-4b44-9757-25e4d86ea19f</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>7ded7c39-cbe1-4b3f-9ba5-c941d350b680</t>
         </is>
@@ -855,55 +861,60 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>d+1+2; db+1+2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Ultimate Tackle</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Ultimate Tackle</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>06b27057-ba76-403e-85c6-5241d4d27973</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>06b27057-ba76-403e-85c6-5241d4d27973</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -920,57 +931,67 @@
           <t>FC+1+2 ,1 ,2 ,1 ,2 ,1</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1,2,1,1,2</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>FC+1+2,1,2,1,1,2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>– Ultimate Punches</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Ultimate Tackle – Ultimate Punches</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>5,5,5,5,5</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>5,5,5,5,5,5</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>22c62dd3-2f75-4092-bad9-4baa879dd867</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>22c62dd3-2f75-4092-bad9-4baa879dd867</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>06b27057-ba76-403e-85c6-5241d4d27973</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -987,57 +1008,67 @@
           <t>FC+1+2 ,2 ,1 ,2 ,1 ,2</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2,1,2,2,1</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>FC+1+2,2,1,2,2,1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>– Ultimate Punches</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Ultimate Tackle – Ultimate Punches</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>5,5,5,5,5</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>5,5,5,5,5,5</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>5693325a-9d43-4c1e-9f0a-37293eb4860d</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>5693325a-9d43-4c1e-9f0a-37293eb4860d</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>06b27057-ba76-403e-85c6-5241d4d27973</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1061,55 +1092,60 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Steel Pedal Drop</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Steel Pedal Drop</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>d51fee9f-9d4e-4225-aa39-2f2d2e364398</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>d51fee9f-9d4e-4225-aa39-2f2d2e364398</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1133,55 +1169,60 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Skull Smash</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Skull Smash</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>9463b80f-225a-4a7a-b350-0a3008c72604</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>9463b80f-225a-4a7a-b350-0a3008c72604</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1205,55 +1246,60 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Reverse Neck Throw</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Reverse Neck Throw</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>cc572ca8-7e2b-4695-be36-969d95d53b5c</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>cc572ca8-7e2b-4695-be36-969d95d53b5c</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1290,130 +1336,135 @@
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="H14" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H14" s="1" t="inlineStr">
+      <c r="I14" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I14" s="1" t="inlineStr">
+      <c r="J14" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J14" s="1" t="inlineStr">
+      <c r="K14" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K14" s="1" t="inlineStr">
+      <c r="L14" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L14" s="1" t="inlineStr">
+      <c r="M14" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M14" s="1" t="inlineStr">
+      <c r="N14" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N14" s="1" t="inlineStr">
+      <c r="O14" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O14" s="1" t="inlineStr">
+      <c r="P14" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P14" s="1" t="inlineStr">
+      <c r="Q14" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q14" s="1" t="inlineStr">
+      <c r="R14" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R14" s="1" t="inlineStr">
+      <c r="S14" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S14" s="1" t="inlineStr">
+      <c r="T14" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T14" s="1" t="inlineStr">
+      <c r="U14" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U14" s="1" t="inlineStr">
+      <c r="V14" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V14" s="1" t="inlineStr">
+      <c r="W14" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W14" s="1" t="inlineStr">
+      <c r="X14" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X14" s="1" t="inlineStr">
+      <c r="Y14" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y14" s="1" t="inlineStr">
+      <c r="Z14" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z14" s="1" t="inlineStr">
+      <c r="AA14" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA14" s="1" t="inlineStr">
+      <c r="AB14" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB14" s="1" t="inlineStr">
+      <c r="AC14" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC14" s="1" t="inlineStr">
+      <c r="AD14" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD14" s="1" t="inlineStr">
+      <c r="AE14" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1430,82 +1481,82 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>dabc7c2c-0b63-4e63-a0c2-aac41cfd7b31</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>d30136ce-acfa-458e-86c3-2cbef646856d</t>
         </is>
@@ -1522,82 +1573,82 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>c879c7a8-a054-42d3-8399-3c96a490030f</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>e235ed17-4e21-473e-9615-4305f408df44</t>
         </is>
@@ -1614,82 +1665,82 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>9e558698-6b63-49f9-afcd-637e0321b01c</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>2d82a396-4060-41e7-941d-75a65ab9d03c</t>
         </is>
@@ -1706,82 +1757,82 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>b468a7bc-7ad2-4a0e-8c34-86e05b4dedcd</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>ecde4b0b-7436-44ac-9b1e-fe82316d0992</t>
         </is>
@@ -1798,82 +1849,82 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>7eb704eb-859c-40f3-9df9-03e81dc11bae</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>2367b18a-e842-45d2-9ed1-de50c9a6d103</t>
         </is>
@@ -1890,82 +1941,82 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>c23932f6-1126-4e92-8ba3-ab0804d0d119</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>6469f633-ab4c-4e47-9286-2551b38e340f</t>
         </is>
@@ -1982,82 +2033,82 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>3ab3928f-5ace-4d1e-8d71-7f8b3ed1168d</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>0b5c31d0-16e4-4050-942d-b655814f638c</t>
         </is>
@@ -2074,82 +2125,82 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>93716291-92fb-4fcb-8928-2124b1da62ab</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>c1deff7b-0570-4086-988c-0a0c759bf306</t>
         </is>
@@ -2166,82 +2217,82 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>70c97f9e-b5ed-44d8-af28-a8bceaf2917f</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>7d9da328-7f3d-496d-b658-e2ee8c0b131d</t>
         </is>
@@ -2258,82 +2309,82 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>65fb314c-3c90-4aa0-a92f-12d4161e72b0</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>cabf096e-34ff-4ce2-bc9d-e9e38da6aa6e</t>
         </is>
@@ -2350,82 +2401,82 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>c5fc3746-bb49-4933-b7bc-1442cdb16bea</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>72d4458f-6f5b-4f73-b5cb-6313202c726e</t>
         </is>
@@ -2442,82 +2493,82 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>cbdce2b8-eec2-40c1-aa00-f79f43e94d4d</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>c1519949-9d2c-4ac2-8c6e-7b654d80d8a7</t>
         </is>
@@ -2534,82 +2585,82 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>a3883459-34dc-475e-ad42-a235e0133396</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>d413488f-9e43-4978-8ba1-bccb0f5d31d6</t>
         </is>
@@ -2626,82 +2677,82 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>cdebfb74-07fd-4ef0-bbe8-d1d0b2e18691</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>cef7e615-556f-40bf-894f-af4836f36539</t>
         </is>
@@ -2718,82 +2769,82 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>529089db-6271-4465-9d73-6e3da9ac5600</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>f5eb2818-c5d1-46d2-b35b-e605c0adee7f</t>
         </is>
@@ -2810,82 +2861,82 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>ca14ccb9-2770-4125-9462-b9443dd76159</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>03ff47c2-2ec9-408b-a4ee-d18718883ab7</t>
         </is>
@@ -2902,82 +2953,82 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>98092a02-87fe-4038-be4a-302dfdfd5ca7</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>8363b13e-edb3-4759-8e33-2c2e72467f26</t>
         </is>
@@ -2994,82 +3045,82 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>b1075b6a-d83f-43ca-8d54-b247f931ea61</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>df4e9be9-76d9-4280-ba88-16512fa611fc</t>
         </is>
@@ -3086,82 +3137,82 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>28e39ff8-57bd-4d7f-8ac8-6b0879b0d7c9</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>80ef5abd-a43c-41d7-83c7-24420d8be88c</t>
         </is>
@@ -3178,82 +3229,82 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>3a4ae7f4-07bf-42b8-9199-900b37f709fa</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>78856454-4f8e-40b8-a516-b0fad76a83ed</t>
         </is>
@@ -3270,82 +3321,82 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>b655d8a4-4885-4036-8a43-ab1b96d0b17f</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>b1d971eb-c2cc-4c9f-99f1-88e369dd1e3f</t>
         </is>
@@ -3362,82 +3413,82 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>6e6290e2-64f0-4197-9467-c958852dd12e</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>23748fc9-981c-43d8-9c5d-add66fe91500</t>
         </is>
@@ -3454,82 +3505,82 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>689518b2-3561-480f-b9a6-6fec11101390</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>7481a608-d610-44e1-97a3-08748964cfc7</t>
         </is>
@@ -3546,82 +3597,82 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>db496bb3-8568-43ee-bc72-6750a1c3c231</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>45ddfb10-d9f1-4887-80c3-98c8e42246da</t>
         </is>
@@ -3658,130 +3709,135 @@
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F41" s="1" t="inlineStr">
+      <c r="G41" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
+      <c r="H41" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H41" s="1" t="inlineStr">
+      <c r="I41" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I41" s="1" t="inlineStr">
+      <c r="J41" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J41" s="1" t="inlineStr">
+      <c r="K41" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K41" s="1" t="inlineStr">
+      <c r="L41" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L41" s="1" t="inlineStr">
+      <c r="M41" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M41" s="1" t="inlineStr">
+      <c r="N41" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N41" s="1" t="inlineStr">
+      <c r="O41" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O41" s="1" t="inlineStr">
+      <c r="P41" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P41" s="1" t="inlineStr">
+      <c r="Q41" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q41" s="1" t="inlineStr">
+      <c r="R41" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R41" s="1" t="inlineStr">
+      <c r="S41" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S41" s="1" t="inlineStr">
+      <c r="T41" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T41" s="1" t="inlineStr">
+      <c r="U41" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U41" s="1" t="inlineStr">
+      <c r="V41" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V41" s="1" t="inlineStr">
+      <c r="W41" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W41" s="1" t="inlineStr">
+      <c r="X41" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X41" s="1" t="inlineStr">
+      <c r="Y41" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y41" s="1" t="inlineStr">
+      <c r="Z41" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z41" s="1" t="inlineStr">
+      <c r="AA41" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA41" s="1" t="inlineStr">
+      <c r="AB41" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB41" s="1" t="inlineStr">
+      <c r="AC41" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC41" s="1" t="inlineStr">
+      <c r="AD41" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD41" s="1" t="inlineStr">
+      <c r="AE41" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3798,92 +3854,92 @@
           <t>1 &lt;2</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>+1 0</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>+1 0</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>+9 +8</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>+9 +8</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>+9 +8</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>+9 +8</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>5,10</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>5,10</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>eaf6d6d4-ffac-460c-bffc-ca4301e34bcb</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AC42" t="inlineStr">
         <is>
           <t>bb53282c-e1bb-4642-9dcf-e642934c23d2</t>
         </is>
@@ -3900,92 +3956,92 @@
           <t>1 &lt;2 ,4</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>– Stature Kick</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Double Punch – Stature Kick</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>+1 0 -14</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>+9 +8 +2</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>+9 +8 +2</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>5,10,17</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>hhl</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>79441b88-a90d-4483-84a2-13ab3a8cec82</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AC43" t="inlineStr">
         <is>
           <t>79905f71-7cb9-41d9-8130-16dd9dd12454</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
+      <c r="AD43" t="inlineStr">
         <is>
           <t>eaf6d6d4-ffac-460c-bffc-ca4301e34bcb</t>
         </is>
@@ -4002,97 +4058,97 @@
           <t>1 ,1 &lt;2</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Shining Fists</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Shining Fists</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>+1 +1 -17</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>+1 +1 -17</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>+9 +9 KD</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>+9 +9 KD</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>+9 +9 KD</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>+9 +9 KD</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>5,8,18</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>5,8,18</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>You cannot Tag if Kazuya is teamed up with Devil.</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>3d152393-9859-43b1-9a72-b720a6642af6</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>2f676bb0-80d5-4448-a457-57c8b23fd998</t>
         </is>
@@ -4109,97 +4165,97 @@
           <t>1 &lt;2 ,2</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Demon Slayer</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Demon Slayer</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>+1 0 -12</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>+1 0 -12</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>+9 +8 +1</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>+9 +8 +1</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>+9 +8 +1</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>+9 +8 +1</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>5,10,18</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>5,10,18</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>You cannot Tag if Kazuya is teamed up with Devil.</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>f04a8512-5c39-41c8-b345-fea68fb357f2</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>eb47fe50-f1e1-4ccb-8c27-4e96a6721e5f</t>
         </is>
@@ -4216,107 +4272,107 @@
           <t>WS+1 ,2</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Twin Pistons</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Twin Pistons</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>-2 -6</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>-2 -6</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>+9 KD</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>+9 KD</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>+9 KD</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>+9 KD</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>12,15</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>12,15</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>You cannot Tag if Kazuya is teamed up with Devil.</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>1dad3097-4ebf-4696-93fe-22ae259074b9</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>ed3f51fe-a9e8-4132-be33-dd876243cc8d</t>
         </is>
@@ -4333,97 +4389,97 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Entrials Smash</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Entrials Smash</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>06839eea-7f3d-465b-b55b-364a673a2273</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>226504a2-f4ec-4f9d-95d9-74437efc6bef</t>
         </is>
@@ -4440,97 +4496,97 @@
           <t>f,N,d,df+1</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Thunder Godfist</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Thunder Godfist</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>(+1_KD)</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>(+1_KD)</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>(+1_KD)</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>(+1_KD)</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>Damage is 43 on a clean hit and the opponent will be knocked down.</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>380cc9da-6995-415c-b1fe-a8c6881346f2</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>bc2935fa-8885-4789-a97c-343d424f38a3</t>
         </is>
@@ -4547,92 +4603,92 @@
           <t>f,N,d,df+1 ,3</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>– Mid Kick</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Thunder Godfist – Mid Kick</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>-14 -14</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>(+1_KD) KD</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>(+1_KD) KD</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>29,20</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>3f49b136-d176-49a2-ad2e-3c69443e72b3</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>1e5c45f6-b929-4609-bbca-4910d1493e47</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>380cc9da-6995-415c-b1fe-a8c6881346f2</t>
         </is>
@@ -4649,92 +4705,92 @@
           <t>f,N,d,df+1 ,4</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>– Hell Sweep</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Thunder Godfist – Hell Sweep</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>-23</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>-14 -23</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>(+1_KD) KD</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>(+1_KD) KD</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>29,12</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>8c05cb79-6c33-45f8-9036-8f6b0456d29f</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>1b75613a-0697-460a-b28f-2d522c7df9d0</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
+      <c r="AD50" t="inlineStr">
         <is>
           <t>380cc9da-6995-415c-b1fe-a8c6881346f2</t>
         </is>
@@ -4751,97 +4807,97 @@
           <t>f+1+2</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Glorious Demon Fist</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Glorious Demon Fist</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>JG CFS</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>3672d72c-aca2-4931-afbd-e64a7a604781</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>515afcf0-6971-4e0e-a6cb-e16e13ffc029</t>
         </is>
@@ -4858,57 +4914,57 @@
           <t>f,N</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Kazuya Mist Step</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Kazuya Mist Step</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>Kazuya will Side Step left if f is tapped on an odd frame number. He will Side Step right on an even frame number.</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>cde7e0d9-7402-4be1-b51f-88972e604afa</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
+      <c r="AC52" t="inlineStr">
         <is>
           <t>a351a497-f9c7-44be-8061-8ac626147706</t>
         </is>
@@ -4925,97 +4981,97 @@
           <t>f,N,df+1</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>– Thunder Godfist</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Kazuya Mist Step – Thunder Godfist</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>(+1_KD)</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>(+1_KD)</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>(+1_KD)</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>(+1_KD)</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>-,29</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>-m</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>Damage is 43 on a clean hit and the opponent will be knocked down.</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>87593a73-6aaa-4ea2-9472-28e9e9f96354</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>8e900acf-c931-4fff-8937-e6b5cad4c1d1</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
+      <c r="AD53" t="inlineStr">
         <is>
           <t>cde7e0d9-7402-4be1-b51f-88972e604afa</t>
         </is>
@@ -5032,87 +5088,87 @@
           <t>f,N,3</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>– Mid Kick</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Kazuya Mist Step – Mid Kick</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>-,10</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>-m</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>c13bcc8c-9d61-4dd4-8060-01be7d5c61db</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AC54" t="inlineStr">
         <is>
           <t>14c90472-3515-488d-8533-54675a085cc1</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
+      <c r="AD54" t="inlineStr">
         <is>
           <t>cde7e0d9-7402-4be1-b51f-88972e604afa</t>
         </is>
@@ -5129,87 +5185,87 @@
           <t>f,N,4</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>– Hell Sweep</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Kazuya Mist Step – Hell Sweep</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>-23</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>-23</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>-,12</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>-L</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>68c45ef4-1d45-49af-9f54-16c678bd57a4</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
+      <c r="AC55" t="inlineStr">
         <is>
           <t>e11aeaa8-0936-4ada-862e-ce21550e9c28</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
+      <c r="AD55" t="inlineStr">
         <is>
           <t>cde7e0d9-7402-4be1-b51f-88972e604afa</t>
         </is>
@@ -5226,102 +5282,102 @@
           <t>f,N,df+2</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>– Wind Godfist</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Kazuya Mist Step – Wind Godfist</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>-,25</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>-s</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>ea94dfdd-be8a-470d-9ff3-0f20e41082e7</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
+      <c r="AC56" t="inlineStr">
         <is>
           <t>137a6b9c-ff11-4a05-a93f-8d72b94b8ce9</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
+      <c r="AD56" t="inlineStr">
         <is>
           <t>cde7e0d9-7402-4be1-b51f-88972e604afa</t>
         </is>
@@ -5338,92 +5394,92 @@
           <t>f,N,DF+4 ,4</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>– Hell Sweeps</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Kazuya Mist Step – Hell Sweeps</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>-23 -23</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>-23 -23</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>-5 KD</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>-5 KD</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>-5 KD</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>-5 KD</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>12,12</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>-,12,12</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>-LL</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>53161ddb-ad93-49c9-91cb-7781c1102ebc</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
+      <c r="AC57" t="inlineStr">
         <is>
           <t>ccd0bf42-466e-4976-a8a4-f67cdc7e1bd5</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
+      <c r="AD57" t="inlineStr">
         <is>
           <t>cde7e0d9-7402-4be1-b51f-88972e604afa</t>
         </is>
@@ -5440,102 +5496,102 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Demon Gut Punch</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Demon Gut Punch</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>JG FS DSc</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>Only stuns on a clean hit and the damage will be 37.</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>e35d9b82-5382-46a8-83b8-3d32541df84e</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
+      <c r="AC58" t="inlineStr">
         <is>
           <t>43fca246-a64e-4efc-ba6c-d666ff941ba9</t>
         </is>
@@ -5552,102 +5608,102 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Gut Punch</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Gut Punch</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>JGc CFSc</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>Requires a clean hit and a counter hit before it stuns. Damage will be around 46 depending on the counter hit frame.</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>d18e5ca7-e5fe-4f85-996d-dbc84ee7b475</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
+      <c r="AC59" t="inlineStr">
         <is>
           <t>3c7e846f-2088-4048-8673-9df96136d2c0</t>
         </is>
@@ -5664,92 +5720,92 @@
           <t>2 ,2</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Demon Backhand Spin</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Demon Backhand Spin</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>0 -13</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>0 -13</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>+9 -2</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>+9 -2</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>+9 -2</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>+9 -2</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>12,21</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>12,21</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>bbea0adc-a90f-4569-b977-b9aa9b563710</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
+      <c r="AC60" t="inlineStr">
         <is>
           <t>d5cf8da3-2cff-448e-8ec4-c734bdf32d40</t>
         </is>
@@ -5766,97 +5822,97 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Soul Thrust</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Soul Thrust</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>MS GB KNDc</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>ab824e6b-d136-41fe-a288-9da84e80347c</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
+      <c r="AC61" t="inlineStr">
         <is>
           <t>5bda9c82-bc11-4ff6-8929-d0aa2f74b245</t>
         </is>
@@ -5873,107 +5929,107 @@
           <t>f,N,d,df+2</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Wind Godfist</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Wind Godfist</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>You cannot Tag if Kazuya is teamed up with Devil.</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>6becb413-f42b-44b0-a455-45f8b9af6127</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
+      <c r="AC62" t="inlineStr">
         <is>
           <t>52877781-47d5-411e-9781-1a32421642e9</t>
         </is>
@@ -5990,92 +6046,92 @@
           <t>f,f+3</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Split Axe Kick</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Split Axe Kick</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>cc98172d-79d1-420f-9d98-a06568742609</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
+      <c r="AC63" t="inlineStr">
         <is>
           <t>ec412abd-a44c-42a8-82a4-cb9aa51ba144</t>
         </is>
@@ -6099,95 +6155,100 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>f,f,f+3</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>Leaping Slash Kick</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Leaping Slash Kick</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>b4b44b08-1bb3-4f0a-8eb3-ab25ff9a00a3</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
+      <c r="AC64" t="inlineStr">
         <is>
           <t>5e251313-8a19-4874-a96c-109461eb0051</t>
         </is>
@@ -6204,102 +6265,102 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Axe Kick</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Axe Kick</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>Causes KS on a crouching opponent and SLD on CH.</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>b844282c-2130-4fb7-a6a1-a635b4cff153</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
+      <c r="AC65" t="inlineStr">
         <is>
           <t>bf92443b-3e02-44bc-9d21-a875e6f7ef9d</t>
         </is>
@@ -6316,92 +6377,92 @@
           <t>df+4 &lt;4</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Delay Tsunami Kick</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Delay Tsunami Kick</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>-9 -15</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>-9 -15</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>+2 -4</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>+2 -4</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>+2 -4</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>+2 -4</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>10,18</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>10,18</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="V66" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AB66" t="inlineStr">
         <is>
           <t>a8d26073-b300-4795-a492-cefefeedde7c</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
+      <c r="AC66" t="inlineStr">
         <is>
           <t>f166e13c-af23-4ab0-a60c-5bd5b02d74fb</t>
         </is>
@@ -6418,92 +6479,92 @@
           <t>WS+4 ,4</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Quick Tsunami Kick</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Quick Tsunami Kick</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>-3 -15</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>-3 -15</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>+8 -4</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>+8 -4</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>+8 -4</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>+8 -4</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>10,18</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>10,18</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="AA67" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>35931985-deaa-4576-ab8a-eabbba23208f</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
+      <c r="AC67" t="inlineStr">
         <is>
           <t>12384989-d69b-4712-8abb-9058044f8b93</t>
         </is>
@@ -6520,102 +6581,102 @@
           <t>f,N,d,DF+4 ,4</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Hell Sweeps</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Hell Sweeps</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>-23 -23</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>-23 -23</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>-5 KD</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>-5 KD</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>-5 KD</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>-5 KD</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>15,12</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>15,12</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>Does 18 damage on a clean hit if only one hell sweep is executed. And 12 damge if it hits far out.</t>
         </is>
       </c>
-      <c r="AA68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>06dab072-fb33-439b-b4b5-54251349c412</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
+      <c r="AC68" t="inlineStr">
         <is>
           <t>a979315a-ad81-4637-a55f-fdeb4c95681d</t>
         </is>
@@ -6632,97 +6693,97 @@
           <t>uf,N+4</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Hop Kick</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Hop Kick</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="V69" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="AA69" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>97c259dd-4178-4427-a434-a3548af60dd8</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
+      <c r="AC69" t="inlineStr">
         <is>
           <t>7cb09500-96b5-4960-bf38-ec1b66cba088</t>
         </is>
@@ -6746,95 +6807,100 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>uf+4,4,4,4</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>Spinning Demon</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Spinning Demon</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>1 1 1 1</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>-12 -12 -26 -10</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>-12 -12 -26 -10</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>KD KD KD KD</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>KD KD KD KD</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>KD KD KD KD</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>KD KD KD KD</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>25,15,12,25</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>25,15,12,25</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>hLLm</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="V70" t="inlineStr">
         <is>
           <t>hLLm</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>491795a6-56e5-4121-85bc-d908832c12e4</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
+      <c r="AC70" t="inlineStr">
         <is>
           <t>5321a922-8513-4dbf-b96d-29a726cf5cfe</t>
         </is>
@@ -6858,95 +6924,100 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>4~3</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>Demon Scissor</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Demon Scissor</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>KND</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="V71" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>415cd305-1fc2-4b2b-a4b5-7381c9a6424d</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
+      <c r="AC71" t="inlineStr">
         <is>
           <t>914a3891-3f14-4bb5-af8b-150227f087a8</t>
         </is>
@@ -6963,92 +7034,92 @@
           <t>db+4</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Stature Kick</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Stature Kick</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="V72" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>29f8152a-3ff9-46f2-aecd-c46fb2749281</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
+      <c r="AC72" t="inlineStr">
         <is>
           <t>3e2c9b6b-9b2f-4de9-b0b2-99b50a3fd4cf</t>
         </is>
@@ -7085,130 +7156,135 @@
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F75" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F75" s="1" t="inlineStr">
+      <c r="G75" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G75" s="1" t="inlineStr">
+      <c r="H75" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H75" s="1" t="inlineStr">
+      <c r="I75" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I75" s="1" t="inlineStr">
+      <c r="J75" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J75" s="1" t="inlineStr">
+      <c r="K75" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K75" s="1" t="inlineStr">
+      <c r="L75" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L75" s="1" t="inlineStr">
+      <c r="M75" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M75" s="1" t="inlineStr">
+      <c r="N75" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N75" s="1" t="inlineStr">
+      <c r="O75" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O75" s="1" t="inlineStr">
+      <c r="P75" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P75" s="1" t="inlineStr">
+      <c r="Q75" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q75" s="1" t="inlineStr">
+      <c r="R75" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R75" s="1" t="inlineStr">
+      <c r="S75" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S75" s="1" t="inlineStr">
+      <c r="T75" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T75" s="1" t="inlineStr">
+      <c r="U75" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U75" s="1" t="inlineStr">
+      <c r="V75" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V75" s="1" t="inlineStr">
+      <c r="W75" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W75" s="1" t="inlineStr">
+      <c r="X75" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X75" s="1" t="inlineStr">
+      <c r="Y75" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y75" s="1" t="inlineStr">
+      <c r="Z75" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z75" s="1" t="inlineStr">
+      <c r="AA75" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA75" s="1" t="inlineStr">
+      <c r="AB75" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB75" s="1" t="inlineStr">
+      <c r="AC75" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC75" s="1" t="inlineStr">
+      <c r="AD75" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD75" s="1" t="inlineStr">
+      <c r="AE75" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -7225,82 +7301,82 @@
           <t>b+1+4</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Lightning Godfist</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Lightning Godfist</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="V76" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>8104883b-67cc-48fc-ace7-d7fe5d386bce</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
+      <c r="AC76" t="inlineStr">
         <is>
           <t>0f01574c-831e-4b63-bfae-e3a8f63a939a</t>
         </is>
@@ -7317,82 +7393,82 @@
           <t>B+1+4</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Lightning Screw Godfist</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Lightning Screw Godfist</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="V77" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>7279f4c9-4e76-4cca-ba82-525cff792fbc</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
+      <c r="AC77" t="inlineStr">
         <is>
           <t>76b603ba-c25c-4f38-a6f3-0e091b62c426</t>
         </is>
@@ -7429,130 +7505,135 @@
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F80" s="1" t="inlineStr">
+      <c r="G80" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G80" s="1" t="inlineStr">
+      <c r="H80" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H80" s="1" t="inlineStr">
+      <c r="I80" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I80" s="1" t="inlineStr">
+      <c r="J80" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J80" s="1" t="inlineStr">
+      <c r="K80" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K80" s="1" t="inlineStr">
+      <c r="L80" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L80" s="1" t="inlineStr">
+      <c r="M80" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
+      <c r="N80" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N80" s="1" t="inlineStr">
+      <c r="O80" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O80" s="1" t="inlineStr">
+      <c r="P80" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P80" s="1" t="inlineStr">
+      <c r="Q80" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q80" s="1" t="inlineStr">
+      <c r="R80" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R80" s="1" t="inlineStr">
+      <c r="S80" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S80" s="1" t="inlineStr">
+      <c r="T80" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T80" s="1" t="inlineStr">
+      <c r="U80" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U80" s="1" t="inlineStr">
+      <c r="V80" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V80" s="1" t="inlineStr">
+      <c r="W80" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W80" s="1" t="inlineStr">
+      <c r="X80" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X80" s="1" t="inlineStr">
+      <c r="Y80" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y80" s="1" t="inlineStr">
+      <c r="Z80" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z80" s="1" t="inlineStr">
+      <c r="AA80" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA80" s="1" t="inlineStr">
+      <c r="AB80" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB80" s="1" t="inlineStr">
+      <c r="AC80" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC80" s="1" t="inlineStr">
+      <c r="AD80" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD80" s="1" t="inlineStr">
+      <c r="AE80" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -7569,47 +7650,47 @@
           <t>f,f+2 ,1 ,2 ,2 ,3 ,4 ,4 ,1 ,2 ,1</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>7,8,6,7,6,11,5,5,8,30</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>7,8,6,7,6,11,5,5,8,30</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>hh"hh"mm"Lhmm</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="V81" t="inlineStr">
         <is>
           <t>hh"hh"mm"Lhmm</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>a1af16e4-84f3-4abd-b887-4c65bc756223</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
+      <c r="AC81" t="inlineStr">
         <is>
           <t>a1af16e4-84f3-4abd-b887-4c65bc756223</t>
         </is>
       </c>
-      <c r="AD81" t="inlineStr">
+      <c r="AE81" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -7626,47 +7707,47 @@
           <t>f,f+2 ,1 ,2 ,2 ,3 ,4 ,4 ,3 ,2 ,1</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>7,8,6,7,6,11,5,5,25,30</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>7,8,6,7,6,11,5,5,25,30</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>hh'hh"mm"LL"m!</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="V82" t="inlineStr">
         <is>
           <t>hh'hh"mm"LL"m!</t>
         </is>
       </c>
-      <c r="AA82" t="inlineStr">
+      <c r="AB82" t="inlineStr">
         <is>
           <t>1abe1117-e220-4cde-b7c9-6a59e7c16e8d</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
+      <c r="AC82" t="inlineStr">
         <is>
           <t>1abe1117-e220-4cde-b7c9-6a59e7c16e8d</t>
         </is>
       </c>
-      <c r="AD82" t="inlineStr">
+      <c r="AE82" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -7683,47 +7764,47 @@
           <t>f,f+2 ,1 ,4 ,4 ,2 ,4 ,3 ,2 ,1</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>7,6,7,10,5,7,5,25,30</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>7,6,7,10,5,7,5,25,30</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>hh"mm"sm"L"m!</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="V83" t="inlineStr">
         <is>
           <t>hh"mm"sm"L"m!</t>
         </is>
       </c>
-      <c r="AA83" t="inlineStr">
+      <c r="AB83" t="inlineStr">
         <is>
           <t>ca41b863-8414-4a05-af5c-d5d050d26435</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
+      <c r="AC83" t="inlineStr">
         <is>
           <t>ca41b863-8414-4a05-af5c-d5d050d26435</t>
         </is>
       </c>
-      <c r="AD83" t="inlineStr">
+      <c r="AE83" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
